--- a/technician_forms/020_hvac_preventive_maintenance_form--technician_forms.xlsx
+++ b/technician_forms/020_hvac_preventive_maintenance_form--technician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'routine',_'label':_'routine'}</t>
+          <t>routine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'routine', 'label': 'Routine'}</t>
+          <t>Routine</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'emergency',_'label':_'emergency'}</t>
+          <t>emergency</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'emergency', 'label': 'Emergency'}</t>
+          <t>Emergency</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'not_completed',_'label':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'not completed', 'label': 'Not Completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'chatjim',_'label':_'chatjim'}</t>
+          <t>chatjim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'chatjim', 'label': 'chatjim'}</t>
+          <t>chatjim</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'chatjim',_'label':_'chatjim'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'chatjim', 'label': 'chatjim'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
